--- a/Data_Analysis/Sensitivity analysis/Hybrid/sweep_results_hybrid_G2_task066.xlsx
+++ b/Data_Analysis/Sensitivity analysis/Hybrid/sweep_results_hybrid_G2_task066.xlsx
@@ -100,7 +100,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.85546875" customWidth="true"/>
@@ -251,6 +251,94 @@
         <v>5.4453629913025683</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="0">
+        <v>414</v>
+      </c>
+      <c r="B4" s="0">
+        <v>263</v>
+      </c>
+      <c r="C4" s="0">
+        <v>414</v>
+      </c>
+      <c r="D4" s="0">
+        <v>81.105768228978931</v>
+      </c>
+      <c r="E4" s="0">
+        <v>465.35000000000002</v>
+      </c>
+      <c r="F4" s="0">
+        <v>158.2713917987254</v>
+      </c>
+      <c r="G4" s="0">
+        <v>53456.407738342117</v>
+      </c>
+      <c r="H4" s="0">
+        <v>-8709.7611760447999</v>
+      </c>
+      <c r="I4" s="0">
+        <v>5.7599999999999998</v>
+      </c>
+      <c r="J4" s="0">
+        <v>15.18</v>
+      </c>
+      <c r="K4" s="0">
+        <v>2.3650000000000002</v>
+      </c>
+      <c r="L4" s="0">
+        <v>3.395</v>
+      </c>
+      <c r="M4" s="0">
+        <v>300.01457776920245</v>
+      </c>
+      <c r="N4" s="0">
+        <v>5.4453629913026287</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0">
+        <v>414</v>
+      </c>
+      <c r="B5" s="0">
+        <v>264</v>
+      </c>
+      <c r="C5" s="0">
+        <v>414</v>
+      </c>
+      <c r="D5" s="0">
+        <v>81.105768232969496</v>
+      </c>
+      <c r="E5" s="0">
+        <v>465.35000000000002</v>
+      </c>
+      <c r="F5" s="0">
+        <v>158.2713917987254</v>
+      </c>
+      <c r="G5" s="0">
+        <v>53456.407738591573</v>
+      </c>
+      <c r="H5" s="0">
+        <v>-8709.7611752510184</v>
+      </c>
+      <c r="I5" s="0">
+        <v>5.7599999999999998</v>
+      </c>
+      <c r="J5" s="0">
+        <v>15.18</v>
+      </c>
+      <c r="K5" s="0">
+        <v>2.3650000000000002</v>
+      </c>
+      <c r="L5" s="0">
+        <v>3.395</v>
+      </c>
+      <c r="M5" s="0">
+        <v>300.01457776919841</v>
+      </c>
+      <c r="N5" s="0">
+        <v>5.4453629913025683</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>